--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$15</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,9 +322,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t xml:space="preserve">Signature
 </t>
   </si>
@@ -366,6 +360,9 @@
   </si>
   <si>
     <t>Extension.value[x].type</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -635,21 +632,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -977,7 +959,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1080,7 +1062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>78</v>
       </c>
@@ -1183,7 +1165,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>86</v>
       </c>
@@ -1286,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>93</v>
       </c>
@@ -1410,22 +1392,22 @@
         <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1485,21 +1467,21 @@
         <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1597,16 +1579,16 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1628,13 +1610,13 @@
         <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1704,10 +1686,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1721,13 +1703,13 @@
         <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>113</v>
@@ -1801,7 +1783,7 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>18</v>
@@ -1826,13 +1808,13 @@
         <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>122</v>
@@ -1906,13 +1888,13 @@
         <v>18</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>127</v>
       </c>
@@ -1937,7 +1919,7 @@
         <v>18</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>128</v>
@@ -2011,13 +1993,13 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>132</v>
       </c>
@@ -2042,7 +2024,7 @@
         <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>133</v>
@@ -2118,13 +2100,13 @@
         <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>139</v>
       </c>
@@ -2223,13 +2205,13 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>148</v>
       </c>
@@ -2326,7 +2308,7 @@
         <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>18</v>
@@ -2351,7 +2333,7 @@
         <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -2431,31 +2413,13 @@
         <v>18</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK15">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI14">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Log Integrity Signature</t>
+    <t>EU AI Log Integrity Signature</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cryptographic signature or verification hash to ensure the integrity, accountability, and non-repudiation of the AI execution audit log.</t>
+    <t>Provides a digital signature and associated metadata to support verification of the integrity and origin of the AI execution audit record.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-log-integrity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
